--- a/TestData/ERPExcelData.xlsx
+++ b/TestData/ERPExcelData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\POM_Framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F95AF33A-D632-4865-A8A0-1F8040DB73D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A3E8F4-5AF9-47B4-9369-C23B529FB4CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{DAACFB09-697F-4255-96E7-855039E0D9CD}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="91">
   <si>
     <t>suppliername</t>
   </si>
@@ -253,92 +253,74 @@
     <t>New Customer4</t>
   </si>
   <si>
-    <t>AddCategory</t>
-  </si>
-  <si>
-    <t>SupplierNumber</t>
-  </si>
-  <si>
     <t>StockNumber</t>
   </si>
   <si>
-    <t>UOMID</t>
-  </si>
-  <si>
-    <t>UOMDescription</t>
-  </si>
-  <si>
-    <t>PurchasingPrice</t>
-  </si>
-  <si>
-    <t>SellingPrice</t>
-  </si>
-  <si>
-    <t>Fr Stock</t>
-  </si>
-  <si>
-    <t>Sec Stock</t>
-  </si>
-  <si>
-    <t>Thr Stock</t>
-  </si>
-  <si>
-    <t>Four Stock</t>
-  </si>
-  <si>
-    <t>Laptops</t>
-  </si>
-  <si>
-    <t>Mobiles</t>
-  </si>
-  <si>
-    <t>Watches</t>
-  </si>
-  <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Dell</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Samsung</t>
-  </si>
-  <si>
-    <t>Rayban</t>
-  </si>
-  <si>
-    <t>Stock available</t>
-  </si>
-  <si>
-    <t>Srock unavailable</t>
-  </si>
-  <si>
     <t>New Stock1</t>
   </si>
   <si>
-    <t>New Stock3</t>
-  </si>
-  <si>
-    <t>New Stock4</t>
-  </si>
-  <si>
     <t>New Stock2</t>
   </si>
   <si>
-    <t>CategoryNameInput</t>
-  </si>
-  <si>
-    <t>StockNameInput</t>
+    <t>stockCategory</t>
+  </si>
+  <si>
+    <t>supplierNumber</t>
+  </si>
+  <si>
+    <t>stockName</t>
+  </si>
+  <si>
+    <t>unitOfMeasurement</t>
+  </si>
+  <si>
+    <t>purchasingPrice</t>
+  </si>
+  <si>
+    <t>sellingPrice</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>First Category</t>
+  </si>
+  <si>
+    <t>Akhilesh1</t>
+  </si>
+  <si>
+    <t>Rice</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>22000</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>Stock 1</t>
+  </si>
+  <si>
+    <t>Akhilesh2</t>
+  </si>
+  <si>
+    <t>22001</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>Stock 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +345,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -401,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
@@ -409,6 +397,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,178 +1104,95 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43A8BA0E-91CD-4DD0-A638-699807828FE4}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:8">
       <c r="A1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="4" t="s">
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" t="s">
         <v>72</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2">
-        <v>7673232</v>
-      </c>
-      <c r="D2">
-        <v>2323232</v>
-      </c>
-      <c r="E2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F2">
-        <v>121212</v>
-      </c>
-      <c r="G2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H2">
-        <v>212121</v>
-      </c>
-      <c r="I2">
-        <v>98998</v>
-      </c>
-      <c r="J2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3">
-        <v>12121212</v>
-      </c>
-      <c r="D3">
-        <v>32323232</v>
-      </c>
-      <c r="E3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3">
-        <v>333333</v>
-      </c>
-      <c r="G3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3">
-        <v>323232</v>
-      </c>
-      <c r="I3">
-        <v>45454</v>
-      </c>
-      <c r="J3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4">
-        <v>2323222</v>
-      </c>
-      <c r="D4">
-        <v>34545454</v>
-      </c>
-      <c r="E4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F4">
-        <v>444444</v>
-      </c>
-      <c r="G4" t="s">
-        <v>89</v>
-      </c>
-      <c r="H4">
-        <v>4343434</v>
-      </c>
-      <c r="I4">
-        <v>54544</v>
-      </c>
-      <c r="J4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C5">
-        <v>42323232</v>
-      </c>
-      <c r="D5">
-        <v>45466444</v>
-      </c>
-      <c r="E5" t="s">
-        <v>88</v>
-      </c>
-      <c r="F5">
-        <v>555555</v>
-      </c>
-      <c r="G5" t="s">
-        <v>89</v>
-      </c>
-      <c r="H5">
-        <v>545454</v>
-      </c>
-      <c r="I5">
-        <v>54545</v>
-      </c>
-      <c r="J5" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
